--- a/recent_attendance.xlsx
+++ b/recent_attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Đỗ Đức Hùng</t>
+          <t>nguyen_tuan_hoang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:58:11</t>
+          <t>12:16:15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -472,7 +472,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>04:40:17</t>
+          <t>12:15:33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -492,7 +492,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -501,7 +501,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>04:29:22</t>
+          <t>12:05:23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>04:14:00</t>
+          <t>11:58:01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>04:12:10</t>
+          <t>11:36:14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,7 +552,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>04:07:25</t>
+          <t>07:58:11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -572,16 +572,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nguyen_tuan_hoang</t>
+          <t>Đỗ Đức Hùng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03:45:13</t>
+          <t>04:40:17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -592,19 +592,119 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Đỗ Đức Hùng</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>04:29:22</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Đỗ Đức Hùng</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>04:14:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Đỗ Đức Hùng</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>04:12:10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Đỗ Đức Hùng</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>04:07:25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nguyen_tuan_hoang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>03:45:13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Đỗ Đức Hùng</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Đỗ Đức Hùng</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>03:44:03</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
